--- a/evaluation_forms/035_escape_room_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/035_escape_room_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1026,17 +1026,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>escape_room_clues_choices</t>
+          <t>escape_room_puzzles_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_clear_at_all</t>
+          <t>very_engaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not clear at all</t>
+          <t>Very engaging</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_engaging</t>
+          <t>somewhat_engaging</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very engaging</t>
+          <t>Somewhat engaging</t>
         </is>
       </c>
     </row>
@@ -1065,46 +1065,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>somewhat_engaging</t>
+          <t>not_engaging_at_all</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somewhat engaging</t>
+          <t>Not engaging at all</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>escape_room_puzzles_choices</t>
+          <t>escape_room_puzzles_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_engaging_at_all</t>
+          <t>word_puzzles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not engaging at all</t>
+          <t>Word puzzles</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>escape_room_puzzles_choices</t>
+          <t>escape_room_puzzles_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_engaging_at_all</t>
+          <t>visual_puzzles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not engaging at all</t>
+          <t>Visual puzzles</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>word_puzzles</t>
+          <t>physical_puzzles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Word puzzles</t>
+          <t>Physical puzzles</t>
         </is>
       </c>
     </row>
@@ -1133,46 +1133,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>visual_puzzles</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Visual puzzles</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>escape_room_puzzles_type_choices</t>
+          <t>escape_room_immersive_environment_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>physical_puzzles</t>
+          <t>veryประก</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Physical puzzles</t>
+          <t>Veryประก</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>escape_room_puzzles_type_choices</t>
+          <t>escape_room_immersive_environment_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1184,95 +1184,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>veryประก</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Veryประก</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>escape_room_immersive_environment_choices</t>
+          <t>escape_room_value_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>escape_room_immersive_environment_choices</t>
+          <t>escape_room_value_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>escape_room_immersive_environment_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>escape_room_value_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>escape_room_value_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
